--- a/data/trans_bre/KIDM_A_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/KIDM_A_R-Estudios-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,43; 12,03</t>
+          <t>1,42; 11,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 6,92</t>
+          <t>-2,74; 6,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 15,49</t>
+          <t>-2,61; 13,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-30,44; 0,0</t>
+          <t>-30,85; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 2,25</t>
+          <t>-2,5; 1,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 1,09</t>
+          <t>-5,06; 0,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 1,81</t>
+          <t>-1,15; 1,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 2,68</t>
+          <t>-1,32; 2,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-78,89; 304,1</t>
+          <t>-83,75; 225,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-76,81; 43,34</t>
+          <t>-79,6; 32,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,08; 2,48</t>
+          <t>-6,68; 2,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 10,6</t>
+          <t>1,28; 10,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,74; 0,49</t>
+          <t>-8,69; 0,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,8</t>
+          <t>0,0; 7,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 2,44</t>
+          <t>-1,41; 2,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 1,94</t>
+          <t>-2,99; 1,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 1,49</t>
+          <t>-1,84; 1,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 1,71</t>
+          <t>-1,92; 1,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-62,28; 238,28</t>
+          <t>-59,43; 223,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-58,81; 83,02</t>
+          <t>-62,01; 72,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-71,16; 184,35</t>
+          <t>-74,28; 166,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 318,49</t>
+          <t>-90,67; 389,1</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/KIDM_A_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/KIDM_A_R-Estudios-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con salud general autopercibida regular o mala (autopercepción menor)</t>
+          <t>Menores cuya salud general autopercibida es regular o mala</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 11,97</t>
+          <t>1,43; 11,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 6,98</t>
+          <t>-2,68; 7,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 13,28</t>
+          <t>-3,19; 14,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-30,85; 0,0</t>
+          <t>-32,61; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 1,8</t>
+          <t>-2,26; 2,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 0,94</t>
+          <t>-5,3; 1,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 1,92</t>
+          <t>-1,36; 1,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 2,69</t>
+          <t>-1,23; 2,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-83,75; 225,8</t>
+          <t>-78,41; 288,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-79,6; 32,59</t>
+          <t>-76,59; 39,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 2,41</t>
+          <t>-7,56; 2,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 10,84</t>
+          <t>1,31; 10,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 0,91</t>
+          <t>-8,1; 0,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,01</t>
+          <t>0,0; 8,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 2,33</t>
+          <t>-1,47; 2,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 1,87</t>
+          <t>-2,68; 2,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 1,36</t>
+          <t>-1,87; 1,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 1,75</t>
+          <t>-1,76; 1,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-59,43; 223,72</t>
+          <t>-58,76; 232,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-62,01; 72,51</t>
+          <t>-57,28; 84,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-74,28; 166,76</t>
+          <t>-74,95; 162,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-90,67; 389,1</t>
+          <t>-94,52; 466,48</t>
         </is>
       </c>
     </row>
